--- a/absensi_wawancara.xlsx
+++ b/absensi_wawancara.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -749,6 +749,39 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>mohammad rafi priyadi</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>081217775383</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>pryadiraffi@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:38:20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
